--- a/spoilers/conversations.xlsx
+++ b/spoilers/conversations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MYDATA\_GIT_REPOS\mcu4\spoilers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798A1E0C-2261-4744-98E8-846984CD5B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1C50C9-6CD4-43EC-BC1C-DF8D19947ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36286,14 +36286,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -36821,7 +36821,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:O474"/>
@@ -36890,7 +36890,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>58</v>
       </c>
@@ -36933,7 +36933,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>58</v>
       </c>
@@ -36974,7 +36974,7 @@
       </c>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>58</v>
       </c>
@@ -37015,7 +37015,7 @@
       </c>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>58</v>
       </c>
@@ -37056,7 +37056,7 @@
       </c>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>58</v>
       </c>
@@ -37097,7 +37097,7 @@
       </c>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>58</v>
       </c>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="39.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>58</v>
       </c>
@@ -37185,7 +37185,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>58</v>
       </c>
@@ -37228,7 +37228,7 @@
       </c>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>58</v>
       </c>
@@ -37267,7 +37267,7 @@
       </c>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>58</v>
       </c>
@@ -37308,7 +37308,7 @@
       </c>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>58</v>
       </c>
@@ -37349,7 +37349,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="9" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" s="9" customFormat="1" ht="39.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>58</v>
       </c>
@@ -37390,7 +37390,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>58</v>
       </c>
@@ -37431,7 +37431,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>58</v>
       </c>
@@ -37472,7 +37472,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="39.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>58</v>
       </c>
@@ -37517,7 +37517,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>58</v>
       </c>
@@ -37558,7 +37558,7 @@
       </c>
       <c r="O17" s="4"/>
     </row>
-    <row r="18" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>58</v>
       </c>
@@ -37599,7 +37599,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>58</v>
       </c>
@@ -37640,7 +37640,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>58</v>
       </c>
@@ -37681,7 +37681,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>58</v>
       </c>
@@ -37722,7 +37722,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>58</v>
       </c>
@@ -37761,7 +37761,7 @@
       </c>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>58</v>
       </c>
@@ -37801,7 +37801,7 @@
       </c>
       <c r="O23" s="4"/>
     </row>
-    <row r="24" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>58</v>
       </c>
@@ -37841,7 +37841,7 @@
       </c>
       <c r="O24" s="4"/>
     </row>
-    <row r="25" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>58</v>
       </c>
@@ -37881,7 +37881,7 @@
       </c>
       <c r="O25" s="4"/>
     </row>
-    <row r="26" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
         <v>58</v>
       </c>
@@ -37921,7 +37921,7 @@
       </c>
       <c r="O26" s="4"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>58</v>
       </c>
@@ -37960,7 +37960,7 @@
       </c>
       <c r="O27" s="4"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>58</v>
       </c>
@@ -37999,7 +37999,7 @@
       </c>
       <c r="O28" s="4"/>
     </row>
-    <row r="29" spans="1:15" s="11" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" s="11" customFormat="1" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20" t="s">
         <v>58</v>
       </c>
@@ -38040,7 +38040,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20" t="s">
         <v>58</v>
       </c>
@@ -38081,7 +38081,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:15" s="11" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" s="11" customFormat="1" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20" t="s">
         <v>58</v>
       </c>
@@ -38121,7 +38121,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>58</v>
       </c>
@@ -38984,7 +38984,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
         <v>248</v>
       </c>
@@ -39023,7 +39023,7 @@
       <c r="N52" s="5"/>
       <c r="O52" s="5"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="23" t="s">
         <v>248</v>
       </c>
@@ -39047,7 +39047,7 @@
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5">
-        <f>INT((1/COUNTIF(B:B,B53))*100)</f>
+        <f t="shared" ref="I53:I91" si="0">INT((1/COUNTIF(B:B,B53))*100)</f>
         <v>16</v>
       </c>
       <c r="J53" s="5" t="s">
@@ -39065,7 +39065,7 @@
       </c>
       <c r="O53" s="5"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
         <v>248</v>
       </c>
@@ -39091,7 +39091,7 @@
         <v>73</v>
       </c>
       <c r="I54" s="5">
-        <f>INT((1/COUNTIF(B:B,B54))*100)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="J54" s="5" t="s">
@@ -39111,7 +39111,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
         <v>248</v>
       </c>
@@ -39137,7 +39137,7 @@
         <v>77</v>
       </c>
       <c r="I55" s="5">
-        <f>INT((1/COUNTIF(B:B,B55))*100)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="J55" s="5" t="s">
@@ -39153,7 +39153,7 @@
       <c r="N55" s="5"/>
       <c r="O55" s="5"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
         <v>248</v>
       </c>
@@ -39177,7 +39177,7 @@
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5">
-        <f>INT((1/COUNTIF(B:B,B56))*100)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="J56" s="5" t="s">
@@ -39195,7 +39195,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
         <v>248</v>
       </c>
@@ -39219,7 +39219,7 @@
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5">
-        <f>INT((1/COUNTIF(B:B,B57))*100)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="J57" s="5" t="s">
@@ -39235,7 +39235,7 @@
       <c r="N57" s="5"/>
       <c r="O57" s="5"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="24" t="s">
         <v>277</v>
       </c>
@@ -39260,7 +39260,7 @@
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5">
-        <f>INT((1/COUNTIF(B:B,B58))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J58" s="24" t="s">
@@ -39277,7 +39277,7 @@
       <c r="N58" s="5"/>
       <c r="O58" s="5"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="24" t="s">
         <v>277</v>
       </c>
@@ -39302,7 +39302,7 @@
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5">
-        <f>INT((1/COUNTIF(B:B,B59))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J59" s="24" t="s">
@@ -39312,14 +39312,14 @@
         <v>283</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f t="shared" ref="L59:L98" si="0">B59&amp;": "&amp;K59</f>
+        <f t="shared" ref="L59:L98" si="1">B59&amp;": "&amp;K59</f>
         <v>Browning: I strive to live an honest life!</v>
       </c>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
       <c r="O59" s="5"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="24" t="s">
         <v>277</v>
       </c>
@@ -39344,7 +39344,7 @@
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5">
-        <f>INT((1/COUNTIF(B:B,B60))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J60" s="24" t="s">
@@ -39354,14 +39354,14 @@
         <v>316</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Browning: It is rooted in Knowledge and Courage.</v>
       </c>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
       <c r="O60" s="5"/>
     </row>
-    <row r="61" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
         <v>277</v>
       </c>
@@ -39386,7 +39386,7 @@
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5">
-        <f>INT((1/COUNTIF(B:B,B61))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J61" s="25" t="s">
@@ -39396,14 +39396,14 @@
         <v>344</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Calabrini: Yes several types of potions are sold here!</v>
       </c>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
       <c r="O61" s="5"/>
     </row>
-    <row r="62" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="s">
         <v>277</v>
       </c>
@@ -39428,7 +39428,7 @@
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5">
-        <f>INT((1/COUNTIF(B:B,B62))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J62" s="24" t="s">
@@ -39438,14 +39438,14 @@
         <v>348</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Calabrini: The housekeeper at the inn is very chatty.</v>
       </c>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
       <c r="O62" s="5"/>
     </row>
-    <row r="63" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="s">
         <v>277</v>
       </c>
@@ -39470,7 +39470,7 @@
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5">
-        <f>INT((1/COUNTIF(B:B,B63))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J63" s="24" t="s">
@@ -39480,14 +39480,14 @@
         <v>345</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Calabrini: I bear greetings from the HONEST town of Moonglow.</v>
       </c>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
       <c r="O63" s="5"/>
     </row>
-    <row r="64" spans="1:15" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" ht="21.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="24" t="s">
         <v>277</v>
       </c>
@@ -39512,7 +39512,7 @@
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5">
-        <f>INT((1/COUNTIF(B:B,B64))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J64" s="25" t="s">
@@ -39522,14 +39522,14 @@
         <v>284</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Christen: Honest friends are few!</v>
       </c>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
     </row>
-    <row r="65" spans="1:15" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="21.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="24" t="s">
         <v>277</v>
       </c>
@@ -39554,7 +39554,7 @@
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5">
-        <f>INT((1/COUNTIF(B:B,B65))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J65" s="24" t="s">
@@ -39564,14 +39564,14 @@
         <v>319</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Christen: Imma feeling gooood!</v>
       </c>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
     </row>
-    <row r="66" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="24" t="s">
         <v>277</v>
       </c>
@@ -39596,7 +39596,7 @@
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5">
-        <f>INT((1/COUNTIF(B:B,B66))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J66" s="24" t="s">
@@ -39606,14 +39606,14 @@
         <v>285</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Christen: My friend William knows where the rune of honesty is.</v>
       </c>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
     </row>
-    <row r="67" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="24" t="s">
         <v>277</v>
       </c>
@@ -39638,7 +39638,7 @@
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5">
-        <f>INT((1/COUNTIF(B:B,B67))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J67" s="24" t="s">
@@ -39648,14 +39648,14 @@
         <v>349</v>
       </c>
       <c r="L67" s="26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Christen: Hey, don't open Rebelias' personal chests. That's not honest!</v>
       </c>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
       <c r="O67" s="5"/>
     </row>
-    <row r="68" spans="1:15" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="21.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="24" t="s">
         <v>277</v>
       </c>
@@ -39680,7 +39680,7 @@
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5">
-        <f>INT((1/COUNTIF(B:B,B68))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J68" s="24" t="s">
@@ -39690,14 +39690,14 @@
         <v>286</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Christen: The housekeeping nitwit.</v>
       </c>
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
       <c r="O68" s="5"/>
     </row>
-    <row r="69" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="24" t="s">
         <v>277</v>
       </c>
@@ -39722,7 +39722,7 @@
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5">
-        <f>INT((1/COUNTIF(B:B,B69))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J69" s="24" t="s">
@@ -39732,14 +39732,14 @@
         <v>287</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Cromwell: A few honest men are better than numbers!</v>
       </c>
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
       <c r="O69" s="5"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="24" t="s">
         <v>277</v>
       </c>
@@ -39764,7 +39764,7 @@
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5">
-        <f>INT((1/COUNTIF(B:B,B70))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J70" s="24" t="s">
@@ -39774,14 +39774,14 @@
         <v>288</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Cromwell: I speak of the virtues of honesty!</v>
       </c>
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
       <c r="O70" s="5"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="24" t="s">
         <v>277</v>
       </c>
@@ -39806,7 +39806,7 @@
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5">
-        <f>INT((1/COUNTIF(B:B,B71))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J71" s="24" t="s">
@@ -39816,14 +39816,14 @@
         <v>289</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Cromwell: The mantra for Honesty is ’AHM’.</v>
       </c>
       <c r="M71" s="5"/>
       <c r="N71" s="5"/>
       <c r="O71" s="5"/>
     </row>
-    <row r="72" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="24" t="s">
         <v>277</v>
       </c>
@@ -39848,7 +39848,7 @@
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5">
-        <f>INT((1/COUNTIF(B:B,B72))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J72" s="24" t="s">
@@ -39858,14 +39858,14 @@
         <v>342</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Mariah: Yes, I hope to go on a great quest, one day!</v>
       </c>
       <c r="M72" s="5"/>
       <c r="N72" s="5"/>
       <c r="O72" s="5"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="24" t="s">
         <v>277</v>
       </c>
@@ -39890,7 +39890,7 @@
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5">
-        <f>INT((1/COUNTIF(B:B,B73))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J73" s="24" t="s">
@@ -39900,14 +39900,14 @@
         <v>341</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Mariah: I tend to the pond fish. It's honest work.</v>
       </c>
       <c r="M73" s="5"/>
       <c r="N73" s="5"/>
       <c r="O73" s="5"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="24" t="s">
         <v>277</v>
       </c>
@@ -39932,7 +39932,7 @@
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5">
-        <f>INT((1/COUNTIF(B:B,B74))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J74" s="24" t="s">
@@ -39942,14 +39942,14 @@
         <v>290</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Mariah: The quest of the avatar is noble indeed!</v>
       </c>
       <c r="M74" s="5"/>
       <c r="N74" s="5"/>
       <c r="O74" s="5"/>
     </row>
-    <row r="75" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" ht="39.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="24" t="s">
         <v>277</v>
       </c>
@@ -39974,7 +39974,7 @@
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5">
-        <f>INT((1/COUNTIF(B:B,B75))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J75" s="24" t="s">
@@ -39984,14 +39984,14 @@
         <v>317</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Patric the Humble Shepherd: Humility is not derived from any of the four principles.</v>
       </c>
       <c r="M75" s="5"/>
       <c r="N75" s="5"/>
       <c r="O75" s="5"/>
     </row>
-    <row r="76" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="39.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="24" t="s">
         <v>277</v>
       </c>
@@ -40016,7 +40016,7 @@
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5">
-        <f>INT((1/COUNTIF(B:B,B76))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J76" s="24" t="s">
@@ -40026,14 +40026,14 @@
         <v>318</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Patric the Humble Shepherd: Humility is to act while remaining humble.</v>
       </c>
       <c r="M76" s="5"/>
       <c r="N76" s="5"/>
       <c r="O76" s="5"/>
     </row>
-    <row r="77" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="39.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="24" t="s">
         <v>277</v>
       </c>
@@ -40058,7 +40058,7 @@
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5">
-        <f>INT((1/COUNTIF(B:B,B77))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J77" s="24" t="s">
@@ -40068,14 +40068,14 @@
         <v>291</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Patric the Humble Shepherd: I am a meek shepherd.</v>
       </c>
       <c r="M77" s="5"/>
       <c r="N77" s="5"/>
       <c r="O77" s="5"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="24" t="s">
         <v>277</v>
       </c>
@@ -40100,7 +40100,7 @@
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5">
-        <f>INT((1/COUNTIF(B:B,B78))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J78" s="24" t="s">
@@ -40110,14 +40110,14 @@
         <v>292</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Rebelias: Evil still exists in our hearts and souls!</v>
       </c>
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
       <c r="O78" s="5"/>
     </row>
-    <row r="79" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="24" t="s">
         <v>277</v>
       </c>
@@ -40142,7 +40142,7 @@
       </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5">
-        <f>INT((1/COUNTIF(B:B,B79))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J79" s="24" t="s">
@@ -40152,14 +40152,14 @@
         <v>328</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Rebelias: Speak the truth always and shame evil forces!</v>
       </c>
       <c r="M79" s="5"/>
       <c r="N79" s="5"/>
       <c r="O79" s="5"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="24" t="s">
         <v>277</v>
       </c>
@@ -40184,7 +40184,7 @@
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5">
-        <f>INT((1/COUNTIF(B:B,B80))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J80" s="24" t="s">
@@ -40194,14 +40194,14 @@
         <v>293</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Rebelias: I live an honest life as a mystic wizard.</v>
       </c>
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
       <c r="O80" s="5"/>
     </row>
-    <row r="81" spans="1:15" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" ht="21.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="29" t="s">
         <v>277</v>
       </c>
@@ -40226,7 +40226,7 @@
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5">
-        <f>INT((1/COUNTIF(B:B,B81))*100)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="J81" s="29" t="s">
@@ -40236,14 +40236,14 @@
         <v>294</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Scatu: I am the Proprietor of Inn</v>
       </c>
       <c r="M81" s="5"/>
       <c r="N81" s="5"/>
       <c r="O81" s="5"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="24" t="s">
         <v>277</v>
       </c>
@@ -40268,7 +40268,7 @@
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5">
-        <f>INT((1/COUNTIF(B:B,B82))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J82" s="24" t="s">
@@ -40278,14 +40278,14 @@
         <v>295</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shakespeare: Corruption wins not more than honesty!</v>
       </c>
       <c r="M82" s="5"/>
       <c r="N82" s="5"/>
       <c r="O82" s="5"/>
     </row>
-    <row r="83" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="24" t="s">
         <v>277</v>
       </c>
@@ -40310,7 +40310,7 @@
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5">
-        <f>INT((1/COUNTIF(B:B,B83))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J83" s="24" t="s">
@@ -40320,14 +40320,14 @@
         <v>296</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shakespeare: Remember, there is no terror in threats for I am strong in honesty!</v>
       </c>
       <c r="M83" s="5"/>
       <c r="N83" s="5"/>
       <c r="O83" s="5"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="24" t="s">
         <v>277</v>
       </c>
@@ -40352,7 +40352,7 @@
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5">
-        <f>INT((1/COUNTIF(B:B,B84))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J84" s="24" t="s">
@@ -40362,14 +40362,14 @@
         <v>297</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shakespeare: I create tales of honesty.</v>
       </c>
       <c r="M84" s="5"/>
       <c r="N84" s="5"/>
       <c r="O84" s="5"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="24" t="s">
         <v>277</v>
       </c>
@@ -40394,7 +40394,7 @@
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5">
-        <f>INT((1/COUNTIF(B:B,B85))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J85" s="29" t="s">
@@ -40404,14 +40404,14 @@
         <v>298</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shakespeare: A wise wizard.</v>
       </c>
       <c r="M85" s="5"/>
       <c r="N85" s="5"/>
       <c r="O85" s="5"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="24" t="s">
         <v>277</v>
       </c>
@@ -40436,7 +40436,7 @@
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5">
-        <f>INT((1/COUNTIF(B:B,B86))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J86" s="24" t="s">
@@ -40446,14 +40446,14 @@
         <v>274</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shakespeare: Shakespeare</v>
       </c>
       <c r="M86" s="5"/>
       <c r="N86" s="5"/>
       <c r="O86" s="5"/>
     </row>
-    <row r="87" spans="1:15" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" ht="21.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="s">
         <v>277</v>
       </c>
@@ -40478,7 +40478,7 @@
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5">
-        <f>INT((1/COUNTIF(B:B,B87))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J87" s="24" t="s">
@@ -40488,14 +40488,14 @@
         <v>299</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shazom: I will soon die.</v>
       </c>
       <c r="M87" s="5"/>
       <c r="N87" s="5"/>
       <c r="O87" s="5"/>
     </row>
-    <row r="88" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="24" t="s">
         <v>277</v>
       </c>
@@ -40520,7 +40520,7 @@
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5">
-        <f>INT((1/COUNTIF(B:B,B88))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J88" s="24" t="s">
@@ -40530,14 +40530,14 @@
         <v>300</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shazom: I am apprentice to the great wizard Nigel!</v>
       </c>
       <c r="M88" s="5"/>
       <c r="N88" s="5"/>
       <c r="O88" s="5"/>
     </row>
-    <row r="89" spans="1:15" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" ht="21.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="24" t="s">
         <v>277</v>
       </c>
@@ -40562,7 +40562,7 @@
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5">
-        <f>INT((1/COUNTIF(B:B,B89))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J89" s="29" t="s">
@@ -40572,14 +40572,14 @@
         <v>301</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shazom: A dying young wizard.</v>
       </c>
       <c r="M89" s="5"/>
       <c r="N89" s="5"/>
       <c r="O89" s="5"/>
     </row>
-    <row r="90" spans="1:15" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" ht="21.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="24" t="s">
         <v>277</v>
       </c>
@@ -40604,7 +40604,7 @@
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5">
-        <f>INT((1/COUNTIF(B:B,B90))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J90" s="24" t="s">
@@ -40614,14 +40614,14 @@
         <v>275</v>
       </c>
       <c r="L90" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shazom: Shazom</v>
       </c>
       <c r="M90" s="5"/>
       <c r="N90" s="5"/>
       <c r="O90" s="5"/>
     </row>
-    <row r="91" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="24" t="s">
         <v>277</v>
       </c>
@@ -40646,7 +40646,7 @@
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5">
-        <f>INT((1/COUNTIF(B:B,B91))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J91" s="24" t="s">
@@ -40656,14 +40656,14 @@
         <v>302</v>
       </c>
       <c r="L91" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shazom: I will soon need to use the spell he calls ’recall’.</v>
       </c>
       <c r="M91" s="5"/>
       <c r="N91" s="5"/>
       <c r="O91" s="5"/>
     </row>
-    <row r="92" spans="1:15" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" ht="21.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="24" t="s">
         <v>277</v>
       </c>
@@ -40697,14 +40697,14 @@
         <v>303</v>
       </c>
       <c r="L92" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>William: Pretty good.</v>
       </c>
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
       <c r="O92" s="5"/>
     </row>
-    <row r="93" spans="1:15" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" ht="21.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="24" t="s">
         <v>277</v>
       </c>
@@ -40738,14 +40738,14 @@
         <v>304</v>
       </c>
       <c r="L93" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>William: A Nitwit eating a sandwich.</v>
       </c>
       <c r="M93" s="5"/>
       <c r="N93" s="5"/>
       <c r="O93" s="5"/>
     </row>
-    <row r="94" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="24" t="s">
         <v>277</v>
       </c>
@@ -40779,14 +40779,14 @@
         <v>305</v>
       </c>
       <c r="L94" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>William: Search for the rune of honesty near Mariah’s gold chest!</v>
       </c>
       <c r="M94" s="5"/>
       <c r="N94" s="5"/>
       <c r="O94" s="5"/>
     </row>
-    <row r="95" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="24" t="s">
         <v>277</v>
       </c>
@@ -40820,14 +40820,14 @@
         <v>306</v>
       </c>
       <c r="L95" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>William: It’s a peanut butter and grape jelly on lightly toasted bread!</v>
       </c>
       <c r="M95" s="5"/>
       <c r="N95" s="5"/>
       <c r="O95" s="5"/>
     </row>
-    <row r="96" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="29" t="s">
         <v>277</v>
       </c>
@@ -40862,14 +40862,14 @@
         <v>307</v>
       </c>
       <c r="L96" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shaman: I am the Proprietor of Sage Deli, here.</v>
       </c>
       <c r="M96" s="5"/>
       <c r="N96" s="5"/>
       <c r="O96" s="5"/>
     </row>
-    <row r="97" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" ht="26.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="29" t="s">
         <v>277</v>
       </c>
@@ -40904,14 +40904,14 @@
         <v>308</v>
       </c>
       <c r="L97" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Harmony: I am the Proprietor of The Healer shoppe.</v>
       </c>
       <c r="M97" s="5"/>
       <c r="N97" s="5"/>
       <c r="O97" s="5"/>
     </row>
-    <row r="98" spans="1:15" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" ht="21.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="27" t="s">
         <v>277</v>
       </c>
@@ -40946,14 +40946,14 @@
         <v>309</v>
       </c>
       <c r="L98" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Margot: I am the Propriety of Magical Herbs</v>
       </c>
       <c r="M98" s="5"/>
       <c r="N98" s="5"/>
       <c r="O98" s="5"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>350</v>
       </c>
@@ -40992,7 +40992,7 @@
       <c r="N99" s="5"/>
       <c r="O99" s="5"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>350</v>
       </c>
@@ -41031,7 +41031,7 @@
       <c r="N100" s="5"/>
       <c r="O100" s="5"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>350</v>
       </c>
@@ -41070,7 +41070,7 @@
       <c r="N101" s="5"/>
       <c r="O101" s="5"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>350</v>
       </c>
@@ -41109,7 +41109,7 @@
       <c r="N102" s="5"/>
       <c r="O102" s="5"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>350</v>
       </c>
@@ -41150,7 +41150,7 @@
       </c>
       <c r="O103" s="5"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>350</v>
       </c>
@@ -41189,7 +41189,7 @@
       <c r="N104" s="5"/>
       <c r="O104" s="5"/>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>350</v>
       </c>
@@ -41230,7 +41230,7 @@
       </c>
       <c r="O105" s="5"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>350</v>
       </c>
@@ -41271,7 +41271,7 @@
       </c>
       <c r="O106" s="5"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>350</v>
       </c>
@@ -41312,7 +41312,7 @@
       </c>
       <c r="O107" s="5"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>350</v>
       </c>
@@ -41351,7 +41351,7 @@
       <c r="N108" s="5"/>
       <c r="O108" s="5"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>350</v>
       </c>
@@ -41390,7 +41390,7 @@
       <c r="N109" s="5"/>
       <c r="O109" s="5"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>350</v>
       </c>
@@ -41431,7 +41431,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>350</v>
       </c>
@@ -41470,7 +41470,7 @@
       <c r="N111" s="5"/>
       <c r="O111" s="5"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>350</v>
       </c>
@@ -41511,7 +41511,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>350</v>
       </c>
@@ -41552,7 +41552,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>350</v>
       </c>
@@ -41593,7 +41593,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>350</v>
       </c>
@@ -41632,7 +41632,7 @@
       <c r="N115" s="5"/>
       <c r="O115" s="5"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>350</v>
       </c>
@@ -41671,7 +41671,7 @@
       <c r="N116" s="5"/>
       <c r="O116" s="5"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>350</v>
       </c>
@@ -41712,7 +41712,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>350</v>
       </c>
@@ -41755,7 +41755,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>350</v>
       </c>
@@ -41796,7 +41796,7 @@
       </c>
       <c r="O119" s="5"/>
     </row>
-    <row r="120" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
         <v>350</v>
       </c>
@@ -41835,7 +41835,7 @@
       <c r="N120" s="10"/>
       <c r="O120" s="10"/>
     </row>
-    <row r="121" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="10" t="s">
         <v>350</v>
       </c>
@@ -41874,7 +41874,7 @@
       <c r="N121" s="10"/>
       <c r="O121" s="10"/>
     </row>
-    <row r="122" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="10" t="s">
         <v>350</v>
       </c>
@@ -41913,7 +41913,7 @@
       <c r="N122" s="10"/>
       <c r="O122" s="10"/>
     </row>
-    <row r="123" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="10" t="s">
         <v>350</v>
       </c>
@@ -41954,7 +41954,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="10" t="s">
         <v>350</v>
       </c>
@@ -41996,7 +41996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="10" t="s">
         <v>350</v>
       </c>
@@ -42037,7 +42037,7 @@
       </c>
       <c r="O125" s="5"/>
     </row>
-    <row r="126" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="10" t="s">
         <v>350</v>
       </c>
@@ -42076,7 +42076,7 @@
       <c r="N126" s="10"/>
       <c r="O126" s="10"/>
     </row>
-    <row r="127" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="10" t="s">
         <v>350</v>
       </c>
@@ -42115,7 +42115,7 @@
       <c r="N127" s="10"/>
       <c r="O127" s="10"/>
     </row>
-    <row r="128" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="10" t="s">
         <v>350</v>
       </c>
@@ -42154,7 +42154,7 @@
       <c r="N128" s="10"/>
       <c r="O128" s="10"/>
     </row>
-    <row r="129" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="10" t="s">
         <v>350</v>
       </c>
@@ -42193,7 +42193,7 @@
       <c r="N129" s="10"/>
       <c r="O129" s="10"/>
     </row>
-    <row r="130" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="10" t="s">
         <v>350</v>
       </c>
@@ -42232,7 +42232,7 @@
       <c r="N130" s="10"/>
       <c r="O130" s="10"/>
     </row>
-    <row r="131" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="10" t="s">
         <v>350</v>
       </c>
@@ -42271,7 +42271,7 @@
       <c r="N131" s="10"/>
       <c r="O131" s="10"/>
     </row>
-    <row r="132" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="10" t="s">
         <v>350</v>
       </c>
@@ -42310,7 +42310,7 @@
       <c r="N132" s="10"/>
       <c r="O132" s="10"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>350</v>
       </c>
@@ -42349,7 +42349,7 @@
       <c r="N133" s="5"/>
       <c r="O133" s="5"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>350</v>
       </c>
@@ -42388,7 +42388,7 @@
       <c r="N134" s="5"/>
       <c r="O134" s="5"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>350</v>
       </c>
@@ -42427,7 +42427,7 @@
       <c r="N135" s="5"/>
       <c r="O135" s="5"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>350</v>
       </c>
@@ -42468,7 +42468,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>350</v>
       </c>
@@ -42511,7 +42511,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>350</v>
       </c>
@@ -42552,7 +42552,7 @@
       </c>
       <c r="O138" s="5"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>350</v>
       </c>
@@ -42592,7 +42592,7 @@
       <c r="N139" s="5"/>
       <c r="O139" s="5"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>350</v>
       </c>
@@ -42625,14 +42625,14 @@
         <v>447</v>
       </c>
       <c r="L140" s="5" t="str">
-        <f t="shared" ref="L140:L142" si="1">B140&amp;": "&amp;K140</f>
+        <f t="shared" ref="L140:L142" si="2">B140&amp;": "&amp;K140</f>
         <v>Jumar: I am the Proprietor of Duelling Armour.</v>
       </c>
       <c r="M140" s="5"/>
       <c r="N140" s="5"/>
       <c r="O140" s="5"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>350</v>
       </c>
@@ -42665,14 +42665,14 @@
         <v>449</v>
       </c>
       <c r="L141" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Terran: I am the Proprietor of The Keg Tap.</v>
       </c>
       <c r="M141" s="5"/>
       <c r="N141" s="5"/>
       <c r="O141" s="5"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>350</v>
       </c>
@@ -42705,14 +42705,14 @@
         <v>448</v>
       </c>
       <c r="L142" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Zajac: I am the Proprietor of the Honorable Inn.</v>
       </c>
       <c r="M142" s="5"/>
       <c r="N142" s="5"/>
       <c r="O142" s="5"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>350</v>
       </c>
@@ -42755,7 +42755,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>350</v>
       </c>
@@ -42796,7 +42796,7 @@
       </c>
       <c r="O144" s="5"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>512</v>
       </c>
@@ -42835,7 +42835,7 @@
       <c r="N145" s="5"/>
       <c r="O145" s="5"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>512</v>
       </c>
@@ -42874,7 +42874,7 @@
       <c r="N146" s="5"/>
       <c r="O146" s="5"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
         <v>512</v>
       </c>
@@ -42913,7 +42913,7 @@
       <c r="N147" s="5"/>
       <c r="O147" s="5"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>512</v>
       </c>
@@ -42952,7 +42952,7 @@
       <c r="N148" s="5"/>
       <c r="O148" s="5"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>512</v>
       </c>
@@ -42993,7 +42993,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>512</v>
       </c>
@@ -43034,7 +43034,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>512</v>
       </c>
@@ -43075,7 +43075,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="152" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="43" t="s">
         <v>512</v>
       </c>
@@ -43114,7 +43114,7 @@
       <c r="N152" s="43"/>
       <c r="O152" s="43"/>
     </row>
-    <row r="153" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="43" t="s">
         <v>512</v>
       </c>
@@ -43153,7 +43153,7 @@
       <c r="N153" s="43"/>
       <c r="O153" s="43"/>
     </row>
-    <row r="154" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="43" t="s">
         <v>512</v>
       </c>
@@ -43192,7 +43192,7 @@
       <c r="N154" s="43"/>
       <c r="O154" s="43"/>
     </row>
-    <row r="155" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="43" t="s">
         <v>512</v>
       </c>
@@ -43231,7 +43231,7 @@
       <c r="N155" s="43"/>
       <c r="O155" s="43"/>
     </row>
-    <row r="156" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="43" t="s">
         <v>512</v>
       </c>
@@ -43273,7 +43273,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="157" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="43" t="s">
         <v>512</v>
       </c>
@@ -43314,7 +43314,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="158" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="43" t="s">
         <v>512</v>
       </c>
@@ -43355,7 +43355,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>512</v>
       </c>
@@ -43394,7 +43394,7 @@
       <c r="N159" s="5"/>
       <c r="O159" s="5"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>512</v>
       </c>
@@ -43433,7 +43433,7 @@
       <c r="N160" s="5"/>
       <c r="O160" s="5"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
         <v>512</v>
       </c>
@@ -43472,7 +43472,7 @@
       <c r="N161" s="5"/>
       <c r="O161" s="5"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
         <v>512</v>
       </c>
@@ -43511,7 +43511,7 @@
       <c r="N162" s="5"/>
       <c r="O162" s="5"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
         <v>512</v>
       </c>
@@ -43552,7 +43552,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
         <v>512</v>
       </c>
@@ -43593,7 +43593,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>512</v>
       </c>
@@ -43634,7 +43634,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="166" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="43" t="s">
         <v>512</v>
       </c>
@@ -43674,7 +43674,7 @@
       <c r="N166" s="43"/>
       <c r="O166" s="43"/>
     </row>
-    <row r="167" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="43" t="s">
         <v>512</v>
       </c>
@@ -43713,7 +43713,7 @@
       <c r="N167" s="43"/>
       <c r="O167" s="43"/>
     </row>
-    <row r="168" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="43" t="s">
         <v>512</v>
       </c>
@@ -43752,7 +43752,7 @@
       <c r="N168" s="43"/>
       <c r="O168" s="43"/>
     </row>
-    <row r="169" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="43" t="s">
         <v>512</v>
       </c>
@@ -43791,7 +43791,7 @@
       <c r="N169" s="43"/>
       <c r="O169" s="43"/>
     </row>
-    <row r="170" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="43" t="s">
         <v>512</v>
       </c>
@@ -43833,7 +43833,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="171" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="43" t="s">
         <v>512</v>
       </c>
@@ -43874,7 +43874,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="172" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="43" t="s">
         <v>512</v>
       </c>
@@ -43915,7 +43915,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="173" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="43" t="s">
         <v>512</v>
       </c>
@@ -43954,7 +43954,7 @@
       <c r="N173" s="43"/>
       <c r="O173" s="43"/>
     </row>
-    <row r="174" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="43" t="s">
         <v>512</v>
       </c>
@@ -43993,7 +43993,7 @@
       <c r="N174" s="43"/>
       <c r="O174" s="43"/>
     </row>
-    <row r="175" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="43" t="s">
         <v>512</v>
       </c>
@@ -44032,7 +44032,7 @@
       <c r="N175" s="43"/>
       <c r="O175" s="43"/>
     </row>
-    <row r="176" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="43" t="s">
         <v>512</v>
       </c>
@@ -44071,7 +44071,7 @@
       <c r="N176" s="43"/>
       <c r="O176" s="43"/>
     </row>
-    <row r="177" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="43" t="s">
         <v>512</v>
       </c>
@@ -44112,7 +44112,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="178" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="43" t="s">
         <v>512</v>
       </c>
@@ -44154,7 +44154,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="179" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="43" t="s">
         <v>512</v>
       </c>
@@ -44196,7 +44196,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>512</v>
       </c>
@@ -44236,7 +44236,7 @@
       <c r="N180" s="5"/>
       <c r="O180" s="5"/>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
         <v>512</v>
       </c>
@@ -44275,7 +44275,7 @@
       <c r="N181" s="5"/>
       <c r="O181" s="5"/>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>512</v>
       </c>
@@ -44314,7 +44314,7 @@
       <c r="N182" s="5"/>
       <c r="O182" s="5"/>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>512</v>
       </c>
@@ -44353,7 +44353,7 @@
       <c r="N183" s="5"/>
       <c r="O183" s="5"/>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
         <v>512</v>
       </c>
@@ -44394,7 +44394,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
         <v>512</v>
       </c>
@@ -44435,7 +44435,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="5" t="s">
         <v>512</v>
       </c>
@@ -44476,7 +44476,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="187" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="43" t="s">
         <v>512</v>
       </c>
@@ -44515,7 +44515,7 @@
       <c r="N187" s="43"/>
       <c r="O187" s="43"/>
     </row>
-    <row r="188" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="43" t="s">
         <v>512</v>
       </c>
@@ -44554,7 +44554,7 @@
       <c r="N188" s="43"/>
       <c r="O188" s="43"/>
     </row>
-    <row r="189" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="43" t="s">
         <v>512</v>
       </c>
@@ -44593,7 +44593,7 @@
       <c r="N189" s="43"/>
       <c r="O189" s="43"/>
     </row>
-    <row r="190" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="43" t="s">
         <v>512</v>
       </c>
@@ -44632,7 +44632,7 @@
       <c r="N190" s="43"/>
       <c r="O190" s="43"/>
     </row>
-    <row r="191" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="43" t="s">
         <v>512</v>
       </c>
@@ -44673,7 +44673,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="192" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="43" t="s">
         <v>512</v>
       </c>
@@ -44714,7 +44714,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="193" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="43" t="s">
         <v>512</v>
       </c>
@@ -44755,7 +44755,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="194" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="43" t="s">
         <v>512</v>
       </c>
@@ -44794,7 +44794,7 @@
       <c r="N194" s="43"/>
       <c r="O194" s="43"/>
     </row>
-    <row r="195" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="43" t="s">
         <v>512</v>
       </c>
@@ -44833,7 +44833,7 @@
       <c r="N195" s="43"/>
       <c r="O195" s="43"/>
     </row>
-    <row r="196" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="43" t="s">
         <v>512</v>
       </c>
@@ -44872,7 +44872,7 @@
       <c r="N196" s="43"/>
       <c r="O196" s="43"/>
     </row>
-    <row r="197" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="43" t="s">
         <v>512</v>
       </c>
@@ -44911,7 +44911,7 @@
       <c r="N197" s="43"/>
       <c r="O197" s="43"/>
     </row>
-    <row r="198" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="43" t="s">
         <v>512</v>
       </c>
@@ -44952,7 +44952,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="199" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="43" t="s">
         <v>512</v>
       </c>
@@ -44993,7 +44993,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="200" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="43" t="s">
         <v>512</v>
       </c>
@@ -45034,7 +45034,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="201" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="43" t="s">
         <v>512</v>
       </c>
@@ -45073,7 +45073,7 @@
       <c r="N201" s="43"/>
       <c r="O201" s="43"/>
     </row>
-    <row r="202" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="43" t="s">
         <v>512</v>
       </c>
@@ -45112,7 +45112,7 @@
       <c r="N202" s="43"/>
       <c r="O202" s="43"/>
     </row>
-    <row r="203" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="43" t="s">
         <v>512</v>
       </c>
@@ -45151,7 +45151,7 @@
       <c r="N203" s="43"/>
       <c r="O203" s="43"/>
     </row>
-    <row r="204" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="43" t="s">
         <v>512</v>
       </c>
@@ -45190,7 +45190,7 @@
       <c r="N204" s="43"/>
       <c r="O204" s="43"/>
     </row>
-    <row r="205" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="43" t="s">
         <v>512</v>
       </c>
@@ -45231,7 +45231,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="206" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="43" t="s">
         <v>512</v>
       </c>
@@ -45273,7 +45273,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="207" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="43" t="s">
         <v>512</v>
       </c>
@@ -45314,7 +45314,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="5" t="s">
         <v>512</v>
       </c>
@@ -45353,7 +45353,7 @@
       <c r="N208" s="5"/>
       <c r="O208" s="5"/>
     </row>
-    <row r="209" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="43" t="s">
         <v>511</v>
       </c>
@@ -45392,7 +45392,7 @@
       <c r="N209" s="43"/>
       <c r="O209" s="43"/>
     </row>
-    <row r="210" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="43" t="s">
         <v>511</v>
       </c>
@@ -45431,7 +45431,7 @@
       <c r="N210" s="43"/>
       <c r="O210" s="43"/>
     </row>
-    <row r="211" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="43" t="s">
         <v>511</v>
       </c>
@@ -45470,7 +45470,7 @@
       <c r="N211" s="43"/>
       <c r="O211" s="43"/>
     </row>
-    <row r="212" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="43" t="s">
         <v>511</v>
       </c>
@@ -45509,7 +45509,7 @@
       <c r="N212" s="43"/>
       <c r="O212" s="43"/>
     </row>
-    <row r="213" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="43" t="s">
         <v>511</v>
       </c>
@@ -45550,7 +45550,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="214" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="43" t="s">
         <v>511</v>
       </c>
@@ -45583,7 +45583,7 @@
         <v>746</v>
       </c>
       <c r="L214" s="46" t="str">
-        <f t="shared" ref="L214:L215" si="2">B214&amp;": "&amp;K214</f>
+        <f t="shared" ref="L214:L215" si="3">B214&amp;": "&amp;K214</f>
         <v>Faultless: Not good. Pride is a grave sin!</v>
       </c>
       <c r="M214" s="43"/>
@@ -45592,7 +45592,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="215" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="43" t="s">
         <v>511</v>
       </c>
@@ -45625,7 +45625,7 @@
         <v>747</v>
       </c>
       <c r="L215" s="46" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Faultless: Good. Pride is evil's favorite sin!</v>
       </c>
       <c r="M215" s="43"/>
@@ -45634,7 +45634,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="216" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="43" t="s">
         <v>511</v>
       </c>
@@ -45673,7 +45673,7 @@
       <c r="N216" s="43"/>
       <c r="O216" s="43"/>
     </row>
-    <row r="217" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="43" t="s">
         <v>511</v>
       </c>
@@ -45712,7 +45712,7 @@
       <c r="N217" s="43"/>
       <c r="O217" s="43"/>
     </row>
-    <row r="218" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="43" t="s">
         <v>511</v>
       </c>
@@ -45745,14 +45745,14 @@
         <v>762</v>
       </c>
       <c r="L218" s="46" t="str">
-        <f t="shared" ref="L218" si="3">B218&amp;": "&amp;K218</f>
+        <f t="shared" ref="L218" si="4">B218&amp;": "&amp;K218</f>
         <v>Heywood: I haunt eternally.</v>
       </c>
       <c r="M218" s="43"/>
       <c r="N218" s="43"/>
       <c r="O218" s="43"/>
     </row>
-    <row r="219" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="43" t="s">
         <v>511</v>
       </c>
@@ -45791,7 +45791,7 @@
       <c r="N219" s="43"/>
       <c r="O219" s="43"/>
     </row>
-    <row r="220" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="43" t="s">
         <v>511</v>
       </c>
@@ -45832,7 +45832,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="221" spans="1:15" s="45" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" s="45" customFormat="1" ht="22.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="43" t="s">
         <v>511</v>
       </c>
@@ -45873,7 +45873,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="222" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="43" t="s">
         <v>511</v>
       </c>
@@ -45914,7 +45914,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="223" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="43" t="s">
         <v>511</v>
       </c>
@@ -45947,14 +45947,14 @@
         <v>764</v>
       </c>
       <c r="L223" s="46" t="str">
-        <f t="shared" ref="L223:L224" si="4">B223&amp;": "&amp;K223</f>
+        <f t="shared" ref="L223:L224" si="5">B223&amp;": "&amp;K223</f>
         <v>Katrina: I practice humility by meditating here.</v>
       </c>
       <c r="M223" s="43"/>
       <c r="N223" s="43"/>
       <c r="O223" s="43"/>
     </row>
-    <row r="224" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="43" t="s">
         <v>511</v>
       </c>
@@ -45987,14 +45987,14 @@
         <v>765</v>
       </c>
       <c r="L224" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Katrina: She looks like a worn-out survivor.</v>
       </c>
       <c r="M224" s="43"/>
       <c r="N224" s="43"/>
       <c r="O224" s="43"/>
     </row>
-    <row r="225" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="43" t="s">
         <v>511</v>
       </c>
@@ -46033,7 +46033,7 @@
       <c r="N225" s="43"/>
       <c r="O225" s="43"/>
     </row>
-    <row r="226" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="43" t="s">
         <v>511</v>
       </c>
@@ -46072,7 +46072,7 @@
       <c r="N226" s="43"/>
       <c r="O226" s="43"/>
     </row>
-    <row r="227" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="43" t="s">
         <v>511</v>
       </c>
@@ -46113,7 +46113,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="228" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="43" t="s">
         <v>511</v>
       </c>
@@ -46146,7 +46146,7 @@
         <v>749</v>
       </c>
       <c r="L228" s="46" t="str">
-        <f t="shared" ref="L228:L229" si="5">B228&amp;": "&amp;K228</f>
+        <f t="shared" ref="L228:L229" si="6">B228&amp;": "&amp;K228</f>
         <v>Katrina: Undo that or your efforts are meaningless.</v>
       </c>
       <c r="M228" s="43"/>
@@ -46155,7 +46155,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="229" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="43" t="s">
         <v>511</v>
       </c>
@@ -46188,7 +46188,7 @@
         <v>1370</v>
       </c>
       <c r="L229" s="46" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Katrina: The rune of Humility is in the Lycaeum.  Ignore temptations.</v>
       </c>
       <c r="M229" s="43"/>
@@ -46197,7 +46197,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>511</v>
       </c>
@@ -46236,7 +46236,7 @@
       <c r="N230" s="5"/>
       <c r="O230" s="5"/>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
         <v>511</v>
       </c>
@@ -46275,7 +46275,7 @@
       <c r="N231" s="5"/>
       <c r="O231" s="5"/>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="5" t="s">
         <v>511</v>
       </c>
@@ -46314,7 +46314,7 @@
       <c r="N232" s="5"/>
       <c r="O232" s="5"/>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="5" t="s">
         <v>511</v>
       </c>
@@ -46353,7 +46353,7 @@
       <c r="N233" s="5"/>
       <c r="O233" s="5"/>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="5" t="s">
         <v>511</v>
       </c>
@@ -46394,7 +46394,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="235" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="43" t="s">
         <v>511</v>
       </c>
@@ -46433,7 +46433,7 @@
       <c r="N235" s="43"/>
       <c r="O235" s="43"/>
     </row>
-    <row r="236" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="43" t="s">
         <v>511</v>
       </c>
@@ -46472,7 +46472,7 @@
       <c r="N236" s="43"/>
       <c r="O236" s="43"/>
     </row>
-    <row r="237" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="43" t="s">
         <v>511</v>
       </c>
@@ -46511,7 +46511,7 @@
       <c r="N237" s="43"/>
       <c r="O237" s="43"/>
     </row>
-    <row r="238" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="43" t="s">
         <v>511</v>
       </c>
@@ -46552,7 +46552,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="239" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="43" t="s">
         <v>511</v>
       </c>
@@ -46585,7 +46585,7 @@
         <v>750</v>
       </c>
       <c r="L239" s="46" t="str">
-        <f t="shared" ref="L239:L240" si="6">B239&amp;": "&amp;K239</f>
+        <f t="shared" ref="L239:L240" si="7">B239&amp;": "&amp;K239</f>
         <v>Virtuebane: Good! Welcome to Hell.</v>
       </c>
       <c r="M239" s="43"/>
@@ -46594,7 +46594,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="240" spans="1:15" s="45" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" s="45" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="43" t="s">
         <v>511</v>
       </c>
@@ -46627,7 +46627,7 @@
         <v>759</v>
       </c>
       <c r="L240" s="46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Virtuebane: Ah, well.  Sinners are the best winnersss…</v>
       </c>
       <c r="M240" s="43"/>
@@ -46636,7 +46636,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="5" t="s">
         <v>510</v>
       </c>
@@ -46675,7 +46675,7 @@
       <c r="N241" s="5"/>
       <c r="O241" s="5"/>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="5" t="s">
         <v>510</v>
       </c>
@@ -46714,7 +46714,7 @@
       <c r="N242" s="5"/>
       <c r="O242" s="5"/>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="5" t="s">
         <v>510</v>
       </c>
@@ -46753,7 +46753,7 @@
       <c r="N243" s="5"/>
       <c r="O243" s="5"/>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="5" t="s">
         <v>510</v>
       </c>
@@ -46792,7 +46792,7 @@
       <c r="N244" s="5"/>
       <c r="O244" s="5"/>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="5" t="s">
         <v>510</v>
       </c>
@@ -46833,7 +46833,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="5" t="s">
         <v>510</v>
       </c>
@@ -46874,7 +46874,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="5" t="s">
         <v>510</v>
       </c>
@@ -46915,7 +46915,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="5" t="s">
         <v>510</v>
       </c>
@@ -46954,7 +46954,7 @@
       <c r="N248" s="5"/>
       <c r="O248" s="5"/>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="5" t="s">
         <v>510</v>
       </c>
@@ -46993,7 +46993,7 @@
       <c r="N249" s="5"/>
       <c r="O249" s="5"/>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="5" t="s">
         <v>510</v>
       </c>
@@ -47032,7 +47032,7 @@
       <c r="N250" s="5"/>
       <c r="O250" s="5"/>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="5" t="s">
         <v>510</v>
       </c>
@@ -47071,7 +47071,7 @@
       <c r="N251" s="5"/>
       <c r="O251" s="5"/>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="5" t="s">
         <v>510</v>
       </c>
@@ -47112,7 +47112,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="5" t="s">
         <v>510</v>
       </c>
@@ -47153,7 +47153,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="5" t="s">
         <v>510</v>
       </c>
@@ -47194,7 +47194,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="5" t="s">
         <v>510</v>
       </c>
@@ -47233,7 +47233,7 @@
       <c r="N255" s="5"/>
       <c r="O255" s="5"/>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="5" t="s">
         <v>510</v>
       </c>
@@ -47272,7 +47272,7 @@
       <c r="N256" s="5"/>
       <c r="O256" s="5"/>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="5" t="s">
         <v>510</v>
       </c>
@@ -47311,7 +47311,7 @@
       <c r="N257" s="5"/>
       <c r="O257" s="5"/>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="5" t="s">
         <v>510</v>
       </c>
@@ -47350,7 +47350,7 @@
       <c r="N258" s="5"/>
       <c r="O258" s="5"/>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="5" t="s">
         <v>510</v>
       </c>
@@ -47391,7 +47391,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="5" t="s">
         <v>510</v>
       </c>
@@ -47432,7 +47432,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="5" t="s">
         <v>510</v>
       </c>
@@ -47473,7 +47473,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="5" t="s">
         <v>510</v>
       </c>
@@ -47512,7 +47512,7 @@
       <c r="N262" s="5"/>
       <c r="O262" s="5"/>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="5" t="s">
         <v>510</v>
       </c>
@@ -47551,7 +47551,7 @@
       <c r="N263" s="5"/>
       <c r="O263" s="5"/>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="5" t="s">
         <v>510</v>
       </c>
@@ -47590,7 +47590,7 @@
       <c r="N264" s="5"/>
       <c r="O264" s="5"/>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="5" t="s">
         <v>510</v>
       </c>
@@ -47629,7 +47629,7 @@
       <c r="N265" s="5"/>
       <c r="O265" s="5"/>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="5" t="s">
         <v>510</v>
       </c>
@@ -47670,7 +47670,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="5" t="s">
         <v>510</v>
       </c>
@@ -47711,7 +47711,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="5" t="s">
         <v>510</v>
       </c>
@@ -47752,7 +47752,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="5" t="s">
         <v>510</v>
       </c>
@@ -47791,7 +47791,7 @@
       <c r="N269" s="5"/>
       <c r="O269" s="5"/>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="5" t="s">
         <v>510</v>
       </c>
@@ -47830,7 +47830,7 @@
       <c r="N270" s="5"/>
       <c r="O270" s="5"/>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="5" t="s">
         <v>510</v>
       </c>
@@ -47869,7 +47869,7 @@
       <c r="N271" s="5"/>
       <c r="O271" s="5"/>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="5" t="s">
         <v>510</v>
       </c>
@@ -47908,7 +47908,7 @@
       <c r="N272" s="5"/>
       <c r="O272" s="5"/>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="5" t="s">
         <v>510</v>
       </c>
@@ -47949,7 +47949,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="5" t="s">
         <v>510</v>
       </c>
@@ -47990,7 +47990,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="5" t="s">
         <v>510</v>
       </c>
@@ -48031,7 +48031,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="5" t="s">
         <v>510</v>
       </c>
@@ -48070,7 +48070,7 @@
       <c r="N276" s="5"/>
       <c r="O276" s="5"/>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="5" t="s">
         <v>510</v>
       </c>
@@ -48109,7 +48109,7 @@
       <c r="N277" s="5"/>
       <c r="O277" s="5"/>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="5" t="s">
         <v>510</v>
       </c>
@@ -48148,7 +48148,7 @@
       <c r="N278" s="5"/>
       <c r="O278" s="5"/>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="5" t="s">
         <v>510</v>
       </c>
@@ -48187,7 +48187,7 @@
       <c r="N279" s="5"/>
       <c r="O279" s="5"/>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="5" t="s">
         <v>510</v>
       </c>
@@ -48228,7 +48228,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="5" t="s">
         <v>510</v>
       </c>
@@ -48269,7 +48269,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="5" t="s">
         <v>510</v>
       </c>
@@ -48310,7 +48310,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="5" t="s">
         <v>510</v>
       </c>
@@ -48349,7 +48349,7 @@
       <c r="N283" s="5"/>
       <c r="O283" s="5"/>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="5" t="s">
         <v>510</v>
       </c>
@@ -48388,7 +48388,7 @@
       <c r="N284" s="5"/>
       <c r="O284" s="5"/>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="5" t="s">
         <v>510</v>
       </c>
@@ -48427,7 +48427,7 @@
       <c r="N285" s="5"/>
       <c r="O285" s="5"/>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="5" t="s">
         <v>510</v>
       </c>
@@ -48466,7 +48466,7 @@
       <c r="N286" s="5"/>
       <c r="O286" s="5"/>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="5" t="s">
         <v>510</v>
       </c>
@@ -48507,7 +48507,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="5" t="s">
         <v>510</v>
       </c>
@@ -48548,7 +48548,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="5" t="s">
         <v>510</v>
       </c>
@@ -48589,7 +48589,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="5" t="s">
         <v>510</v>
       </c>
@@ -48628,7 +48628,7 @@
       <c r="N290" s="5"/>
       <c r="O290" s="5"/>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="5" t="s">
         <v>510</v>
       </c>
@@ -48667,7 +48667,7 @@
       <c r="N291" s="5"/>
       <c r="O291" s="5"/>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="5" t="s">
         <v>510</v>
       </c>
@@ -48706,7 +48706,7 @@
       <c r="N292" s="5"/>
       <c r="O292" s="5"/>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="5" t="s">
         <v>510</v>
       </c>
@@ -48745,7 +48745,7 @@
       <c r="N293" s="5"/>
       <c r="O293" s="5"/>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="5" t="s">
         <v>510</v>
       </c>
@@ -48786,7 +48786,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="5" t="s">
         <v>510</v>
       </c>
@@ -48827,7 +48827,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="5" t="s">
         <v>510</v>
       </c>
@@ -48868,7 +48868,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="5" t="s">
         <v>510</v>
       </c>
@@ -48907,7 +48907,7 @@
       <c r="N297" s="5"/>
       <c r="O297" s="5"/>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="5" t="s">
         <v>510</v>
       </c>
@@ -48946,7 +48946,7 @@
       <c r="N298" s="5"/>
       <c r="O298" s="5"/>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="5" t="s">
         <v>510</v>
       </c>
@@ -48985,7 +48985,7 @@
       <c r="N299" s="5"/>
       <c r="O299" s="5"/>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="5" t="s">
         <v>510</v>
       </c>
@@ -49024,7 +49024,7 @@
       <c r="N300" s="5"/>
       <c r="O300" s="5"/>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="5" t="s">
         <v>510</v>
       </c>
@@ -49065,7 +49065,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="5" t="s">
         <v>510</v>
       </c>
@@ -49106,7 +49106,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="5" t="s">
         <v>510</v>
       </c>
@@ -49147,7 +49147,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="5" t="s">
         <v>510</v>
       </c>
@@ -49186,7 +49186,7 @@
       <c r="N304" s="5"/>
       <c r="O304" s="5"/>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="5" t="s">
         <v>510</v>
       </c>
@@ -49225,7 +49225,7 @@
       <c r="N305" s="5"/>
       <c r="O305" s="5"/>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="5" t="s">
         <v>510</v>
       </c>
@@ -49264,7 +49264,7 @@
       <c r="N306" s="5"/>
       <c r="O306" s="5"/>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="5" t="s">
         <v>510</v>
       </c>
@@ -49303,7 +49303,7 @@
       <c r="N307" s="5"/>
       <c r="O307" s="5"/>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="5" t="s">
         <v>510</v>
       </c>
@@ -49344,7 +49344,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="5" t="s">
         <v>510</v>
       </c>
@@ -49385,7 +49385,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="5" t="s">
         <v>510</v>
       </c>
@@ -49426,7 +49426,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="5" t="s">
         <v>510</v>
       </c>
@@ -49465,7 +49465,7 @@
       <c r="N311" s="5"/>
       <c r="O311" s="5"/>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="5" t="s">
         <v>510</v>
       </c>
@@ -49504,7 +49504,7 @@
       <c r="N312" s="5"/>
       <c r="O312" s="5"/>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="5" t="s">
         <v>510</v>
       </c>
@@ -49543,7 +49543,7 @@
       <c r="N313" s="5"/>
       <c r="O313" s="5"/>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="5" t="s">
         <v>510</v>
       </c>
@@ -49584,7 +49584,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="5" t="s">
         <v>510</v>
       </c>
@@ -49623,7 +49623,7 @@
       <c r="N315" s="5"/>
       <c r="O315" s="5"/>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="5" t="s">
         <v>510</v>
       </c>
@@ -49662,7 +49662,7 @@
       <c r="N316" s="5"/>
       <c r="O316" s="5"/>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="5" t="s">
         <v>510</v>
       </c>
@@ -49701,7 +49701,7 @@
       <c r="N317" s="5"/>
       <c r="O317" s="5"/>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="5" t="s">
         <v>510</v>
       </c>
@@ -49740,7 +49740,7 @@
       <c r="N318" s="5"/>
       <c r="O318" s="5"/>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="5" t="s">
         <v>510</v>
       </c>
@@ -49781,7 +49781,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="5" t="s">
         <v>510</v>
       </c>
@@ -49822,7 +49822,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="5" t="s">
         <v>510</v>
       </c>
@@ -49863,7 +49863,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="5" t="s">
         <v>248</v>
       </c>
@@ -49902,7 +49902,7 @@
       <c r="N322" s="5"/>
       <c r="O322" s="5"/>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="5" t="s">
         <v>248</v>
       </c>
@@ -49941,7 +49941,7 @@
       <c r="N323" s="5"/>
       <c r="O323" s="5"/>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="5" t="s">
         <v>248</v>
       </c>
@@ -49980,7 +49980,7 @@
       <c r="N324" s="5"/>
       <c r="O324" s="5"/>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="5" t="s">
         <v>248</v>
       </c>
@@ -50019,7 +50019,7 @@
       <c r="N325" s="5"/>
       <c r="O325" s="5"/>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="5" t="s">
         <v>248</v>
       </c>
@@ -50060,7 +50060,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="5" t="s">
         <v>248</v>
       </c>
@@ -50101,7 +50101,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="5" t="s">
         <v>248</v>
       </c>
@@ -50142,7 +50142,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="5" t="s">
         <v>248</v>
       </c>
@@ -50181,7 +50181,7 @@
       <c r="N329" s="5"/>
       <c r="O329" s="5"/>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="5" t="s">
         <v>248</v>
       </c>
@@ -50220,7 +50220,7 @@
       <c r="N330" s="5"/>
       <c r="O330" s="5"/>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="5" t="s">
         <v>248</v>
       </c>
@@ -50259,7 +50259,7 @@
       <c r="N331" s="5"/>
       <c r="O331" s="5"/>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="5" t="s">
         <v>248</v>
       </c>
@@ -50300,7 +50300,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="5" t="s">
         <v>248</v>
       </c>
@@ -50339,7 +50339,7 @@
       <c r="N333" s="5"/>
       <c r="O333" s="5"/>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="5" t="s">
         <v>248</v>
       </c>
@@ -50378,7 +50378,7 @@
       <c r="N334" s="5"/>
       <c r="O334" s="5"/>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="5" t="s">
         <v>248</v>
       </c>
@@ -50417,7 +50417,7 @@
       <c r="N335" s="5"/>
       <c r="O335" s="5"/>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="5" t="s">
         <v>248</v>
       </c>
@@ -50456,7 +50456,7 @@
       <c r="N336" s="5"/>
       <c r="O336" s="5"/>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="5" t="s">
         <v>248</v>
       </c>
@@ -50497,7 +50497,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="5" t="s">
         <v>248</v>
       </c>
@@ -50538,7 +50538,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="5" t="s">
         <v>248</v>
       </c>
@@ -50579,7 +50579,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="5" t="s">
         <v>248</v>
       </c>
@@ -50618,7 +50618,7 @@
       <c r="N340" s="5"/>
       <c r="O340" s="5"/>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="5" t="s">
         <v>248</v>
       </c>
@@ -50657,7 +50657,7 @@
       <c r="N341" s="5"/>
       <c r="O341" s="5"/>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="5" t="s">
         <v>248</v>
       </c>
@@ -50696,7 +50696,7 @@
       <c r="N342" s="5"/>
       <c r="O342" s="5"/>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="5" t="s">
         <v>248</v>
       </c>
@@ -50735,7 +50735,7 @@
       <c r="N343" s="5"/>
       <c r="O343" s="5"/>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="5" t="s">
         <v>248</v>
       </c>
@@ -50776,7 +50776,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="5" t="s">
         <v>248</v>
       </c>
@@ -50817,7 +50817,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="5" t="s">
         <v>248</v>
       </c>
@@ -50858,7 +50858,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="5" t="s">
         <v>248</v>
       </c>
@@ -50897,7 +50897,7 @@
       <c r="N347" s="5"/>
       <c r="O347" s="5"/>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="5" t="s">
         <v>248</v>
       </c>
@@ -50936,7 +50936,7 @@
       <c r="N348" s="5"/>
       <c r="O348" s="5"/>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="5" t="s">
         <v>248</v>
       </c>
@@ -50975,7 +50975,7 @@
       <c r="N349" s="5"/>
       <c r="O349" s="5"/>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="5" t="s">
         <v>248</v>
       </c>
@@ -51014,7 +51014,7 @@
       <c r="N350" s="5"/>
       <c r="O350" s="5"/>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="5" t="s">
         <v>248</v>
       </c>
@@ -51055,7 +51055,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="5" t="s">
         <v>248</v>
       </c>
@@ -51096,7 +51096,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="5" t="s">
         <v>248</v>
       </c>
@@ -51137,7 +51137,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="5" t="s">
         <v>248</v>
       </c>
@@ -51176,7 +51176,7 @@
       <c r="N354" s="5"/>
       <c r="O354" s="5"/>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="5" t="s">
         <v>248</v>
       </c>
@@ -51215,7 +51215,7 @@
       <c r="N355" s="5"/>
       <c r="O355" s="5"/>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="5" t="s">
         <v>248</v>
       </c>
@@ -51254,7 +51254,7 @@
       <c r="N356" s="5"/>
       <c r="O356" s="5"/>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="5" t="s">
         <v>248</v>
       </c>
@@ -51293,7 +51293,7 @@
       <c r="N357" s="5"/>
       <c r="O357" s="5"/>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="5" t="s">
         <v>248</v>
       </c>
@@ -51334,7 +51334,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="5" t="s">
         <v>248</v>
       </c>
@@ -51375,7 +51375,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="5" t="s">
         <v>248</v>
       </c>
@@ -51416,7 +51416,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="5" t="s">
         <v>248</v>
       </c>
@@ -51455,7 +51455,7 @@
       <c r="N361" s="5"/>
       <c r="O361" s="5"/>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="5" t="s">
         <v>248</v>
       </c>
@@ -51494,7 +51494,7 @@
       <c r="N362" s="5"/>
       <c r="O362" s="5"/>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="5" t="s">
         <v>248</v>
       </c>
@@ -51533,7 +51533,7 @@
       <c r="N363" s="5"/>
       <c r="O363" s="5"/>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="5" t="s">
         <v>248</v>
       </c>
@@ -51572,7 +51572,7 @@
       <c r="N364" s="5"/>
       <c r="O364" s="5"/>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="5" t="s">
         <v>248</v>
       </c>
@@ -51613,7 +51613,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="5" t="s">
         <v>248</v>
       </c>
@@ -51654,7 +51654,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="5" t="s">
         <v>248</v>
       </c>
@@ -51695,7 +51695,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="5" t="s">
         <v>248</v>
       </c>
@@ -51734,7 +51734,7 @@
       <c r="N368" s="5"/>
       <c r="O368" s="5"/>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="5" t="s">
         <v>248</v>
       </c>
@@ -51773,7 +51773,7 @@
       <c r="N369" s="5"/>
       <c r="O369" s="5"/>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="5" t="s">
         <v>248</v>
       </c>
@@ -51812,7 +51812,7 @@
       <c r="N370" s="5"/>
       <c r="O370" s="5"/>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="5" t="s">
         <v>248</v>
       </c>
@@ -51851,7 +51851,7 @@
       <c r="N371" s="5"/>
       <c r="O371" s="5"/>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="5" t="s">
         <v>248</v>
       </c>
@@ -51892,7 +51892,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="5" t="s">
         <v>248</v>
       </c>
@@ -51933,7 +51933,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="5" t="s">
         <v>248</v>
       </c>
@@ -51974,7 +51974,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="5" t="s">
         <v>509</v>
       </c>
@@ -52013,7 +52013,7 @@
       <c r="N375" s="5"/>
       <c r="O375" s="5"/>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="5" t="s">
         <v>509</v>
       </c>
@@ -52052,7 +52052,7 @@
       <c r="N376" s="5"/>
       <c r="O376" s="5"/>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="5" t="s">
         <v>509</v>
       </c>
@@ -52091,7 +52091,7 @@
       <c r="N377" s="5"/>
       <c r="O377" s="5"/>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="5" t="s">
         <v>509</v>
       </c>
@@ -52132,7 +52132,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="5" t="s">
         <v>509</v>
       </c>
@@ -52173,7 +52173,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="5" t="s">
         <v>509</v>
       </c>
@@ -52214,7 +52214,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="5" t="s">
         <v>509</v>
       </c>
@@ -52255,7 +52255,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="5" t="s">
         <v>509</v>
       </c>
@@ -52294,7 +52294,7 @@
       <c r="N382" s="5"/>
       <c r="O382" s="5"/>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="5" t="s">
         <v>509</v>
       </c>
@@ -52333,7 +52333,7 @@
       <c r="N383" s="5"/>
       <c r="O383" s="5"/>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="5" t="s">
         <v>509</v>
       </c>
@@ -52372,7 +52372,7 @@
       <c r="N384" s="5"/>
       <c r="O384" s="5"/>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>509</v>
       </c>
@@ -52407,7 +52407,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>509</v>
       </c>
@@ -52445,7 +52445,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>509</v>
       </c>
@@ -52483,7 +52483,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>509</v>
       </c>
@@ -52521,7 +52521,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>509</v>
       </c>
@@ -52556,7 +52556,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>509</v>
       </c>
@@ -52591,7 +52591,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>509</v>
       </c>
@@ -52626,7 +52626,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>509</v>
       </c>
@@ -52661,7 +52661,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>509</v>
       </c>
@@ -52699,7 +52699,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>509</v>
       </c>
@@ -52737,7 +52737,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>509</v>
       </c>
@@ -52775,7 +52775,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>509</v>
       </c>
@@ -52810,7 +52810,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>509</v>
       </c>
@@ -52845,7 +52845,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>509</v>
       </c>
@@ -52880,7 +52880,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>509</v>
       </c>
@@ -52915,7 +52915,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>509</v>
       </c>
@@ -52953,7 +52953,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>509</v>
       </c>
@@ -52991,7 +52991,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>509</v>
       </c>
@@ -53029,7 +53029,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>509</v>
       </c>
@@ -53064,7 +53064,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>509</v>
       </c>
@@ -53099,7 +53099,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>509</v>
       </c>
@@ -53134,7 +53134,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>509</v>
       </c>
@@ -53169,7 +53169,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>509</v>
       </c>
@@ -53207,7 +53207,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>509</v>
       </c>
@@ -53245,7 +53245,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>509</v>
       </c>
@@ -53283,7 +53283,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>509</v>
       </c>
@@ -53318,7 +53318,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>509</v>
       </c>
@@ -53353,7 +53353,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>509</v>
       </c>
@@ -53391,7 +53391,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>509</v>
       </c>
@@ -53429,7 +53429,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>509</v>
       </c>
@@ -53467,7 +53467,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>509</v>
       </c>
@@ -53502,7 +53502,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>509</v>
       </c>
@@ -53537,7 +53537,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>509</v>
       </c>
@@ -53572,7 +53572,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>509</v>
       </c>
@@ -53607,7 +53607,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>509</v>
       </c>
@@ -53645,7 +53645,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>509</v>
       </c>
@@ -53683,7 +53683,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>509</v>
       </c>
@@ -53721,7 +53721,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>509</v>
       </c>
@@ -53756,7 +53756,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>509</v>
       </c>
@@ -53791,7 +53791,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>509</v>
       </c>
@@ -53826,7 +53826,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>509</v>
       </c>
@@ -53861,7 +53861,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>509</v>
       </c>
@@ -53899,7 +53899,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>509</v>
       </c>
@@ -53937,7 +53937,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>509</v>
       </c>
@@ -53975,7 +53975,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>509</v>
       </c>
@@ -54010,7 +54010,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>509</v>
       </c>
@@ -54045,7 +54045,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>509</v>
       </c>
@@ -54080,7 +54080,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>509</v>
       </c>
@@ -54115,7 +54115,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>509</v>
       </c>
@@ -54153,7 +54153,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>509</v>
       </c>
@@ -54191,7 +54191,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>509</v>
       </c>
@@ -54229,7 +54229,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>509</v>
       </c>
@@ -54264,7 +54264,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>509</v>
       </c>
@@ -54299,7 +54299,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>509</v>
       </c>
@@ -54334,7 +54334,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>509</v>
       </c>
@@ -54369,7 +54369,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>509</v>
       </c>
@@ -54407,7 +54407,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>509</v>
       </c>
@@ -54445,7 +54445,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>509</v>
       </c>
@@ -54483,7 +54483,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>509</v>
       </c>
@@ -54518,7 +54518,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>509</v>
       </c>
@@ -54553,7 +54553,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>509</v>
       </c>
@@ -54588,7 +54588,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>509</v>
       </c>
@@ -54623,7 +54623,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>509</v>
       </c>
@@ -54661,7 +54661,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>509</v>
       </c>
@@ -54699,7 +54699,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>509</v>
       </c>
@@ -54737,7 +54737,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>509</v>
       </c>
@@ -54772,7 +54772,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>509</v>
       </c>
@@ -54807,7 +54807,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>509</v>
       </c>
@@ -54842,7 +54842,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>509</v>
       </c>
@@ -54877,7 +54877,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>509</v>
       </c>
@@ -54915,7 +54915,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>509</v>
       </c>
@@ -54953,7 +54953,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>509</v>
       </c>
@@ -54991,7 +54991,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>509</v>
       </c>
@@ -55026,7 +55026,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>509</v>
       </c>
@@ -55061,7 +55061,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>509</v>
       </c>
@@ -55096,7 +55096,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>509</v>
       </c>
@@ -55134,7 +55134,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>509</v>
       </c>
@@ -55169,7 +55169,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>509</v>
       </c>
@@ -55204,7 +55204,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>509</v>
       </c>
@@ -55239,7 +55239,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>509</v>
       </c>
@@ -55274,7 +55274,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>509</v>
       </c>
@@ -55312,7 +55312,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>509</v>
       </c>
@@ -55350,7 +55350,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>509</v>
       </c>
@@ -55388,7 +55388,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>509</v>
       </c>
@@ -55423,7 +55423,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>509</v>
       </c>
@@ -55458,7 +55458,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>509</v>
       </c>
@@ -55493,7 +55493,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>509</v>
       </c>
@@ -55528,7 +55528,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>509</v>
       </c>
@@ -55566,7 +55566,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>509</v>
       </c>
@@ -55604,7 +55604,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>509</v>
       </c>
@@ -55643,7 +55643,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O474" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:O474" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Jhelom"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="K1:K105 K110:K111 K113:K142 K144:K1048576">
     <cfRule type="expression" dxfId="8" priority="16">
       <formula>"&gt;len(20)"</formula>
@@ -55689,7 +55695,7 @@
       <formula>"&gt;len(20)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G29 G32:G384" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Statement,Question,Statement-Roll"</formula1>
     </dataValidation>

--- a/spoilers/conversations.xlsx
+++ b/spoilers/conversations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MYDATA\_GIT_REPOS\mcu4\spoilers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AABCEE6-E0E6-4BC9-BD68-16C493184F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1DF0D3-C086-448F-978D-5C92D672C688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4756" uniqueCount="1461">
   <si>
     <t>Game-Level Conversation List</t>
   </si>
@@ -4381,6 +4381,60 @@
   </si>
   <si>
     <t>Estrol: Then speak to the judge in Yew!</t>
+  </si>
+  <si>
+    <t>Rooms</t>
+  </si>
+  <si>
+    <t>3, 6, or 9 gold nuggets -- finer stays cost more.</t>
+  </si>
+  <si>
+    <t>Estro: Rooms for rent -- 3, 6, or 9 gold nuggets, finer stays cost more. See my trades.</t>
+  </si>
+  <si>
+    <t>gold-&gt;copper (3)</t>
+  </si>
+  <si>
+    <t>Estro: Here's your change -- room's ready, door shuts in 20s.</t>
+  </si>
+  <si>
+    <t>Opens room-1 door, 20s auto-checkout; if occupied, refunds 3 gold instead and declines</t>
+  </si>
+  <si>
+    <t>gold-&gt;copper (6)</t>
+  </si>
+  <si>
+    <t>Opens room-2 door, same pattern, refund 6 gold if occupied</t>
+  </si>
+  <si>
+    <t>gold-&gt;copper (9)</t>
+  </si>
+  <si>
+    <t>Opens room-3 door, same pattern, refund 9 gold if occupied</t>
+  </si>
+  <si>
+    <t>OK, room 2. Here's your change.</t>
+  </si>
+  <si>
+    <t>OK, room 1. Here's your change.</t>
+  </si>
+  <si>
+    <t>OK, room 3. Here's your change.</t>
+  </si>
+  <si>
+    <t>Butch</t>
+  </si>
+  <si>
+    <t>Barkeep</t>
+  </si>
+  <si>
+    <t>Want Food?</t>
+  </si>
+  <si>
+    <t>We've got a fine selection of goods.</t>
+  </si>
+  <si>
+    <t>Butch: We've got a fine selection of goods.</t>
   </si>
 </sst>
 </file>
@@ -37150,7 +37204,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:O495"/>
+  <dimension ref="A1:O499"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -39373,7 +39427,7 @@
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5">
-        <f>INT((1/COUNTIF(B:B,B53))*100)</f>
+        <f t="shared" ref="I53:I91" si="0">INT((1/COUNTIF(B:B,B53))*100)</f>
         <v>16</v>
       </c>
       <c r="J53" s="5" t="s">
@@ -39417,7 +39471,7 @@
         <v>73</v>
       </c>
       <c r="I54" s="5">
-        <f>INT((1/COUNTIF(B:B,B54))*100)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="J54" s="5" t="s">
@@ -39463,7 +39517,7 @@
         <v>77</v>
       </c>
       <c r="I55" s="5">
-        <f>INT((1/COUNTIF(B:B,B55))*100)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="J55" s="5" t="s">
@@ -39503,7 +39557,7 @@
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5">
-        <f>INT((1/COUNTIF(B:B,B56))*100)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="J56" s="5" t="s">
@@ -39545,7 +39599,7 @@
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5">
-        <f>INT((1/COUNTIF(B:B,B57))*100)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="J57" s="5" t="s">
@@ -39586,7 +39640,7 @@
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5">
-        <f>INT((1/COUNTIF(B:B,B58))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J58" s="24" t="s">
@@ -39628,7 +39682,7 @@
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5">
-        <f>INT((1/COUNTIF(B:B,B59))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J59" s="24" t="s">
@@ -39638,7 +39692,7 @@
         <v>283</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f t="shared" ref="L59:L98" si="0">B59&amp;": "&amp;K59</f>
+        <f t="shared" ref="L59:L98" si="1">B59&amp;": "&amp;K59</f>
         <v>Browning: I strive to live an honest life!</v>
       </c>
       <c r="M59" s="5"/>
@@ -39670,7 +39724,7 @@
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5">
-        <f>INT((1/COUNTIF(B:B,B60))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J60" s="24" t="s">
@@ -39680,7 +39734,7 @@
         <v>316</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Browning: It is rooted in Knowledge and Courage.</v>
       </c>
       <c r="M60" s="5"/>
@@ -39712,7 +39766,7 @@
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5">
-        <f>INT((1/COUNTIF(B:B,B61))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J61" s="25" t="s">
@@ -39722,7 +39776,7 @@
         <v>344</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Calabrini: Yes several types of potions are sold here!</v>
       </c>
       <c r="M61" s="5"/>
@@ -39754,7 +39808,7 @@
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5">
-        <f>INT((1/COUNTIF(B:B,B62))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J62" s="24" t="s">
@@ -39764,7 +39818,7 @@
         <v>348</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Calabrini: The housekeeper at the inn is very chatty.</v>
       </c>
       <c r="M62" s="5"/>
@@ -39796,7 +39850,7 @@
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5">
-        <f>INT((1/COUNTIF(B:B,B63))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J63" s="24" t="s">
@@ -39806,7 +39860,7 @@
         <v>345</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Calabrini: I bear greetings from the HONEST town of Moonglow.</v>
       </c>
       <c r="M63" s="5"/>
@@ -39838,7 +39892,7 @@
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5">
-        <f>INT((1/COUNTIF(B:B,B64))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J64" s="25" t="s">
@@ -39848,7 +39902,7 @@
         <v>284</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Christen: Honest friends are few!</v>
       </c>
       <c r="M64" s="5"/>
@@ -39880,7 +39934,7 @@
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5">
-        <f>INT((1/COUNTIF(B:B,B65))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J65" s="24" t="s">
@@ -39890,7 +39944,7 @@
         <v>319</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Christen: Imma feeling gooood!</v>
       </c>
       <c r="M65" s="5"/>
@@ -39922,7 +39976,7 @@
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5">
-        <f>INT((1/COUNTIF(B:B,B66))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J66" s="24" t="s">
@@ -39932,7 +39986,7 @@
         <v>285</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Christen: My friend William knows where the rune of honesty is.</v>
       </c>
       <c r="M66" s="5"/>
@@ -39964,7 +40018,7 @@
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5">
-        <f>INT((1/COUNTIF(B:B,B67))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J67" s="24" t="s">
@@ -39974,7 +40028,7 @@
         <v>349</v>
       </c>
       <c r="L67" s="26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Christen: Hey, don't open Rebelias' personal chests. That's not honest!</v>
       </c>
       <c r="M67" s="5"/>
@@ -40006,7 +40060,7 @@
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5">
-        <f>INT((1/COUNTIF(B:B,B68))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J68" s="24" t="s">
@@ -40016,7 +40070,7 @@
         <v>286</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Christen: The housekeeping nitwit.</v>
       </c>
       <c r="M68" s="5"/>
@@ -40048,7 +40102,7 @@
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5">
-        <f>INT((1/COUNTIF(B:B,B69))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J69" s="24" t="s">
@@ -40058,7 +40112,7 @@
         <v>287</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Cromwell: A few honest men are better than numbers!</v>
       </c>
       <c r="M69" s="5"/>
@@ -40090,7 +40144,7 @@
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5">
-        <f>INT((1/COUNTIF(B:B,B70))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J70" s="24" t="s">
@@ -40100,7 +40154,7 @@
         <v>288</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Cromwell: I speak of the virtues of honesty!</v>
       </c>
       <c r="M70" s="5"/>
@@ -40132,7 +40186,7 @@
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5">
-        <f>INT((1/COUNTIF(B:B,B71))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J71" s="24" t="s">
@@ -40142,7 +40196,7 @@
         <v>289</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Cromwell: The mantra for Honesty is ’AHM’.</v>
       </c>
       <c r="M71" s="5"/>
@@ -40174,7 +40228,7 @@
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5">
-        <f>INT((1/COUNTIF(B:B,B72))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J72" s="24" t="s">
@@ -40184,7 +40238,7 @@
         <v>342</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Mariah: Yes, I hope to go on a great quest, one day!</v>
       </c>
       <c r="M72" s="5"/>
@@ -40216,7 +40270,7 @@
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5">
-        <f>INT((1/COUNTIF(B:B,B73))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J73" s="24" t="s">
@@ -40226,7 +40280,7 @@
         <v>341</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Mariah: I tend to the pond fish. It's honest work.</v>
       </c>
       <c r="M73" s="5"/>
@@ -40258,7 +40312,7 @@
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5">
-        <f>INT((1/COUNTIF(B:B,B74))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J74" s="24" t="s">
@@ -40268,7 +40322,7 @@
         <v>290</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Mariah: The quest of the avatar is noble indeed!</v>
       </c>
       <c r="M74" s="5"/>
@@ -40300,7 +40354,7 @@
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5">
-        <f>INT((1/COUNTIF(B:B,B75))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J75" s="24" t="s">
@@ -40310,7 +40364,7 @@
         <v>317</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Patric the Humble Shepherd: Humility is not derived from any of the four principles.</v>
       </c>
       <c r="M75" s="5"/>
@@ -40342,7 +40396,7 @@
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5">
-        <f>INT((1/COUNTIF(B:B,B76))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J76" s="24" t="s">
@@ -40352,7 +40406,7 @@
         <v>318</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Patric the Humble Shepherd: Humility is to act while remaining humble.</v>
       </c>
       <c r="M76" s="5"/>
@@ -40384,7 +40438,7 @@
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5">
-        <f>INT((1/COUNTIF(B:B,B77))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J77" s="24" t="s">
@@ -40394,7 +40448,7 @@
         <v>291</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Patric the Humble Shepherd: I am a meek shepherd.</v>
       </c>
       <c r="M77" s="5"/>
@@ -40426,7 +40480,7 @@
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5">
-        <f>INT((1/COUNTIF(B:B,B78))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J78" s="24" t="s">
@@ -40436,7 +40490,7 @@
         <v>292</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Rebelias: Evil still exists in our hearts and souls!</v>
       </c>
       <c r="M78" s="5"/>
@@ -40468,7 +40522,7 @@
       </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5">
-        <f>INT((1/COUNTIF(B:B,B79))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J79" s="24" t="s">
@@ -40478,7 +40532,7 @@
         <v>328</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Rebelias: Speak the truth always and shame evil forces!</v>
       </c>
       <c r="M79" s="5"/>
@@ -40510,7 +40564,7 @@
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5">
-        <f>INT((1/COUNTIF(B:B,B80))*100)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="J80" s="24" t="s">
@@ -40520,7 +40574,7 @@
         <v>293</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Rebelias: I live an honest life as a mystic wizard.</v>
       </c>
       <c r="M80" s="5"/>
@@ -40552,7 +40606,7 @@
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5">
-        <f>INT((1/COUNTIF(B:B,B81))*100)</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="J81" s="29" t="s">
@@ -40562,7 +40616,7 @@
         <v>294</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Scatu: I am the Proprietor of Inn</v>
       </c>
       <c r="M81" s="5"/>
@@ -40594,7 +40648,7 @@
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5">
-        <f>INT((1/COUNTIF(B:B,B82))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J82" s="24" t="s">
@@ -40604,7 +40658,7 @@
         <v>295</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shakespeare: Corruption wins not more than honesty!</v>
       </c>
       <c r="M82" s="5"/>
@@ -40636,7 +40690,7 @@
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5">
-        <f>INT((1/COUNTIF(B:B,B83))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J83" s="24" t="s">
@@ -40646,7 +40700,7 @@
         <v>296</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shakespeare: Remember, there is no terror in threats for I am strong in honesty!</v>
       </c>
       <c r="M83" s="5"/>
@@ -40678,7 +40732,7 @@
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5">
-        <f>INT((1/COUNTIF(B:B,B84))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J84" s="24" t="s">
@@ -40688,7 +40742,7 @@
         <v>297</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shakespeare: I create tales of honesty.</v>
       </c>
       <c r="M84" s="5"/>
@@ -40720,7 +40774,7 @@
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5">
-        <f>INT((1/COUNTIF(B:B,B85))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J85" s="29" t="s">
@@ -40730,7 +40784,7 @@
         <v>298</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shakespeare: A wise wizard.</v>
       </c>
       <c r="M85" s="5"/>
@@ -40762,7 +40816,7 @@
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5">
-        <f>INT((1/COUNTIF(B:B,B86))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J86" s="24" t="s">
@@ -40772,7 +40826,7 @@
         <v>274</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shakespeare: Shakespeare</v>
       </c>
       <c r="M86" s="5"/>
@@ -40804,7 +40858,7 @@
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5">
-        <f>INT((1/COUNTIF(B:B,B87))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J87" s="24" t="s">
@@ -40814,7 +40868,7 @@
         <v>299</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shazom: I will soon die.</v>
       </c>
       <c r="M87" s="5"/>
@@ -40846,7 +40900,7 @@
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5">
-        <f>INT((1/COUNTIF(B:B,B88))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J88" s="24" t="s">
@@ -40856,7 +40910,7 @@
         <v>300</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shazom: I am apprentice to the great wizard Nigel!</v>
       </c>
       <c r="M88" s="5"/>
@@ -40888,7 +40942,7 @@
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5">
-        <f>INT((1/COUNTIF(B:B,B89))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J89" s="29" t="s">
@@ -40898,7 +40952,7 @@
         <v>301</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shazom: A dying young wizard.</v>
       </c>
       <c r="M89" s="5"/>
@@ -40930,7 +40984,7 @@
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5">
-        <f>INT((1/COUNTIF(B:B,B90))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J90" s="24" t="s">
@@ -40940,7 +40994,7 @@
         <v>275</v>
       </c>
       <c r="L90" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shazom: Shazom</v>
       </c>
       <c r="M90" s="5"/>
@@ -40972,7 +41026,7 @@
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5">
-        <f>INT((1/COUNTIF(B:B,B91))*100)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J91" s="24" t="s">
@@ -40982,7 +41036,7 @@
         <v>302</v>
       </c>
       <c r="L91" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shazom: I will soon need to use the spell he calls ’recall’.</v>
       </c>
       <c r="M91" s="5"/>
@@ -41023,7 +41077,7 @@
         <v>303</v>
       </c>
       <c r="L92" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>William: Pretty good.</v>
       </c>
       <c r="M92" s="5"/>
@@ -41064,7 +41118,7 @@
         <v>304</v>
       </c>
       <c r="L93" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>William: A Nitwit eating a sandwich.</v>
       </c>
       <c r="M93" s="5"/>
@@ -41105,7 +41159,7 @@
         <v>305</v>
       </c>
       <c r="L94" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>William: Search for the rune of honesty near Mariah’s gold chest!</v>
       </c>
       <c r="M94" s="5"/>
@@ -41146,7 +41200,7 @@
         <v>306</v>
       </c>
       <c r="L95" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>William: It’s a peanut butter and grape jelly on lightly toasted bread!</v>
       </c>
       <c r="M95" s="5"/>
@@ -41188,7 +41242,7 @@
         <v>307</v>
       </c>
       <c r="L96" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Shaman: I am the Proprietor of Sage Deli, here.</v>
       </c>
       <c r="M96" s="5"/>
@@ -41230,7 +41284,7 @@
         <v>308</v>
       </c>
       <c r="L97" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Harmony: I am the Proprietor of The Healer shoppe.</v>
       </c>
       <c r="M97" s="5"/>
@@ -41272,7 +41326,7 @@
         <v>309</v>
       </c>
       <c r="L98" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Margot: I am the Propriety of Magical Herbs</v>
       </c>
       <c r="M98" s="5"/>
@@ -42951,7 +43005,7 @@
         <v>447</v>
       </c>
       <c r="L140" s="5" t="str">
-        <f t="shared" ref="L140:L142" si="1">B140&amp;": "&amp;K140</f>
+        <f t="shared" ref="L140:L142" si="2">B140&amp;": "&amp;K140</f>
         <v>Jumar: I am the Proprietor of Duelling Armour.</v>
       </c>
       <c r="M140" s="5"/>
@@ -42991,7 +43045,7 @@
         <v>449</v>
       </c>
       <c r="L141" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Terran: I am the Proprietor of The Keg Tap.</v>
       </c>
       <c r="M141" s="5"/>
@@ -43031,7 +43085,7 @@
         <v>448</v>
       </c>
       <c r="L142" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Zajac: I am the Proprietor of the Honorable Inn.</v>
       </c>
       <c r="M142" s="5"/>
@@ -45909,7 +45963,7 @@
         <v>740</v>
       </c>
       <c r="L214" s="46" t="str">
-        <f t="shared" ref="L214:L215" si="2">B214&amp;": "&amp;K214</f>
+        <f t="shared" ref="L214:L215" si="3">B214&amp;": "&amp;K214</f>
         <v>Faultless: Not good. Pride is a grave sin!</v>
       </c>
       <c r="M214" s="43"/>
@@ -45951,7 +46005,7 @@
         <v>741</v>
       </c>
       <c r="L215" s="46" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Faultless: Good. Pride is evil's favorite sin!</v>
       </c>
       <c r="M215" s="43"/>
@@ -46071,7 +46125,7 @@
         <v>756</v>
       </c>
       <c r="L218" s="46" t="str">
-        <f t="shared" ref="L218" si="3">B218&amp;": "&amp;K218</f>
+        <f t="shared" ref="L218" si="4">B218&amp;": "&amp;K218</f>
         <v>Heywood: I haunt eternally.</v>
       </c>
       <c r="M218" s="43"/>
@@ -46273,7 +46327,7 @@
         <v>758</v>
       </c>
       <c r="L223" s="46" t="str">
-        <f t="shared" ref="L223:L224" si="4">B223&amp;": "&amp;K223</f>
+        <f t="shared" ref="L223:L224" si="5">B223&amp;": "&amp;K223</f>
         <v>Katrina: I practice humility by meditating here.</v>
       </c>
       <c r="M223" s="43"/>
@@ -46313,7 +46367,7 @@
         <v>759</v>
       </c>
       <c r="L224" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Katrina: She looks like a worn-out survivor.</v>
       </c>
       <c r="M224" s="43"/>
@@ -46472,7 +46526,7 @@
         <v>743</v>
       </c>
       <c r="L228" s="46" t="str">
-        <f t="shared" ref="L228:L229" si="5">B228&amp;": "&amp;K228</f>
+        <f t="shared" ref="L228:L229" si="6">B228&amp;": "&amp;K228</f>
         <v>Katrina: Undo that or your efforts are meaningless.</v>
       </c>
       <c r="M228" s="43"/>
@@ -46514,7 +46568,7 @@
         <v>1308</v>
       </c>
       <c r="L229" s="46" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Katrina: The rune of Humility is in the Lycaeum.  Ignore temptations.</v>
       </c>
       <c r="M229" s="43"/>
@@ -46911,7 +46965,7 @@
         <v>744</v>
       </c>
       <c r="L239" s="46" t="str">
-        <f t="shared" ref="L239:L240" si="6">B239&amp;": "&amp;K239</f>
+        <f t="shared" ref="L239:L240" si="7">B239&amp;": "&amp;K239</f>
         <v>Virtuebane: Good! Welcome to Hell.</v>
       </c>
       <c r="M239" s="43"/>
@@ -46953,7 +47007,7 @@
         <v>753</v>
       </c>
       <c r="L240" s="46" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Virtuebane: Ah, well.  Sinners are the best winnersss…</v>
       </c>
       <c r="M240" s="43"/>
@@ -56771,11 +56825,198 @@
       </c>
     </row>
     <row r="495" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B495" s="48"/>
+      <c r="A495" t="s">
+        <v>510</v>
+      </c>
+      <c r="B495" s="48" t="s">
+        <v>533</v>
+      </c>
+      <c r="C495" t="s">
+        <v>250</v>
+      </c>
+      <c r="D495" t="s">
+        <v>61</v>
+      </c>
+      <c r="E495" t="s">
+        <v>154</v>
+      </c>
+      <c r="F495" s="16">
+        <v>-1</v>
+      </c>
+      <c r="G495" t="s">
+        <v>81</v>
+      </c>
+      <c r="J495" t="s">
+        <v>1443</v>
+      </c>
+      <c r="K495" t="s">
+        <v>1444</v>
+      </c>
+      <c r="L495" t="s">
+        <v>1445</v>
+      </c>
+      <c r="M495">
+        <v>0</v>
+      </c>
+      <c r="N495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>510</v>
+      </c>
+      <c r="B496" t="s">
+        <v>533</v>
+      </c>
+      <c r="C496" t="s">
+        <v>250</v>
+      </c>
+      <c r="D496" t="s">
+        <v>79</v>
+      </c>
+      <c r="E496" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F496" s="16">
+        <v>-1</v>
+      </c>
+      <c r="G496" t="s">
+        <v>81</v>
+      </c>
+      <c r="K496" t="s">
+        <v>1454</v>
+      </c>
+      <c r="L496" t="s">
+        <v>1447</v>
+      </c>
+      <c r="M496">
+        <v>10</v>
+      </c>
+      <c r="N496">
+        <v>0</v>
+      </c>
+      <c r="O496" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="497" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>510</v>
+      </c>
+      <c r="B497" t="s">
+        <v>533</v>
+      </c>
+      <c r="C497" t="s">
+        <v>250</v>
+      </c>
+      <c r="D497" t="s">
+        <v>79</v>
+      </c>
+      <c r="E497" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F497" s="16">
+        <v>-1</v>
+      </c>
+      <c r="G497" t="s">
+        <v>81</v>
+      </c>
+      <c r="K497" t="s">
+        <v>1453</v>
+      </c>
+      <c r="L497" t="s">
+        <v>1447</v>
+      </c>
+      <c r="M497">
+        <v>10</v>
+      </c>
+      <c r="N497">
+        <v>0</v>
+      </c>
+      <c r="O497" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="498" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>510</v>
+      </c>
+      <c r="B498" t="s">
+        <v>533</v>
+      </c>
+      <c r="C498" t="s">
+        <v>250</v>
+      </c>
+      <c r="D498" t="s">
+        <v>79</v>
+      </c>
+      <c r="E498" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F498" s="16">
+        <v>-1</v>
+      </c>
+      <c r="G498" t="s">
+        <v>81</v>
+      </c>
+      <c r="K498" t="s">
+        <v>1455</v>
+      </c>
+      <c r="L498" t="s">
+        <v>1447</v>
+      </c>
+      <c r="M498">
+        <v>10</v>
+      </c>
+      <c r="N498">
+        <v>0</v>
+      </c>
+      <c r="O498" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="499" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>510</v>
+      </c>
+      <c r="B499" s="48" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D499" t="s">
+        <v>61</v>
+      </c>
+      <c r="E499" t="s">
+        <v>154</v>
+      </c>
+      <c r="F499" s="16">
+        <v>-1</v>
+      </c>
+      <c r="G499" t="s">
+        <v>81</v>
+      </c>
+      <c r="J499" t="s">
+        <v>1458</v>
+      </c>
+      <c r="K499" t="s">
+        <v>1459</v>
+      </c>
+      <c r="L499" t="s">
+        <v>1460</v>
+      </c>
+      <c r="M499">
+        <v>0</v>
+      </c>
+      <c r="N499">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O494" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
-  <conditionalFormatting sqref="K1:K105 K110:K111 K113:K142 K284:K319 K321:K328 K329:L330 K331:K335 K337 K339 K341:K1048576 K144:K282">
+  <conditionalFormatting sqref="K1:K105 K110:K111 K113:K142 K144:K282 K284:K319 K321:K328 K329:L330 K331:K335 K337 K339 L496:L498 K341:K1048576">
     <cfRule type="expression" dxfId="20" priority="48">
       <formula>"&gt;len(20)"</formula>
     </cfRule>

--- a/spoilers/conversations.xlsx
+++ b/spoilers/conversations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MYDATA\_GIT_REPOS\mcu4\spoilers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1DF0D3-C086-448F-978D-5C92D672C688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C03AA7-A219-4B15-92FE-9132E6C08CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4428,13 +4428,13 @@
     <t>Barkeep</t>
   </si>
   <si>
-    <t>Want Food?</t>
-  </si>
-  <si>
-    <t>We've got a fine selection of goods.</t>
-  </si>
-  <si>
-    <t>Butch: We've got a fine selection of goods.</t>
+    <t>Howdy! Hungry?</t>
+  </si>
+  <si>
+    <t>Hungry? We've got a fine selection of goods.</t>
+  </si>
+  <si>
+    <t>Butch: Hungry? We've got a fine selection of goods.</t>
   </si>
 </sst>
 </file>
